--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557268.1743175344</v>
+        <v>557268</v>
       </c>
       <c r="R2" t="n">
-        <v>6291749.046957554</v>
+        <v>6291749</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557268.1743175344</v>
+        <v>557268</v>
       </c>
       <c r="R3" t="n">
-        <v>6291749.046957554</v>
+        <v>6291749</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74605035</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74602556</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35252-2025 artfynd.xlsx
+++ b/artfynd/A 35252-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74605035</v>
+        <v>74602556</v>
       </c>
       <c r="B2" t="n">
-        <v>97543</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G8b 3230. SOM: Lycopodium clavatum. LEG: Lennart Stenberg, Jörgen Andersson, Curt Mossberg</t>
+          <t>Smålands flora 2007: KOO: 4G8b 3230. SOM: Lycopodium annotinum. LEG: Lennart Stenberg, Jörgen Andersson, Curt Mossberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74602556</v>
+        <v>74605035</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G8b 3230. SOM: Lycopodium annotinum. LEG: Lennart Stenberg, Jörgen Andersson, Curt Mossberg</t>
+          <t>Smålands flora 2007: KOO: 4G8b 3230. SOM: Lycopodium clavatum. LEG: Lennart Stenberg, Jörgen Andersson, Curt Mossberg</t>
         </is>
       </c>
       <c r="AD3" t="b">
